--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/bio-bio.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/bio-bio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M161"/>
+  <dimension ref="A1:M162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>853.91</v>
+        <v>846.6799999999999</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>9166.110000000001</v>
+        <v>9119.01</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>374.05</v>
+        <v>372.13</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>57238.77</v>
+        <v>56667.52</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1298.5</v>
+        <v>1291.4</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>22460.14</v>
+        <v>22209.9</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1631.06</v>
+        <v>1622.12</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2150.58</v>
+        <v>2138.8</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>76146.39999999999</v>
+        <v>76049.48</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>22443.15</v>
+        <v>22414.59</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>673.5700000000001</v>
+        <v>672.71</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>23794.01</v>
+        <v>24052.81</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>60917.12</v>
+        <v>61579.68</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>128.25</v>
+        <v>130.46</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>726.73</v>
+        <v>739.27</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1025.97</v>
+        <v>1043.68</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>470.24</v>
+        <v>478.35</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>56.41</v>
+        <v>56.67</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>21302.72</v>
+        <v>21401.93</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>26524.21</v>
+        <v>26647.74</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1068.72</v>
+        <v>1066.83</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2975.29</v>
+        <v>2963.03</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>25613.62</v>
+        <v>25508.05</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>40467.25</v>
+        <v>40300.46</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1715.63</v>
+        <v>1708.56</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>13894.18</v>
+        <v>13836.91</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5418.42</v>
+        <v>5446.4</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>24732.35</v>
+        <v>24906.9</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>39961.63</v>
+        <v>40243.67</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>155.54</v>
+        <v>153.53</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>18067.53</v>
+        <v>17887.76</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>12798.71</v>
+        <v>12752.82</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>10563.17</v>
+        <v>10525.29</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>4832.15</v>
+        <v>4814.82</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>24231.5</v>
+        <v>24144.61</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1375.48</v>
+        <v>1372.5</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>21066.34</v>
+        <v>20822.54</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>21703.2</v>
+        <v>21452.03</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>7649.82</v>
+        <v>7643.67</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>18576.95</v>
+        <v>18661.13</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3370.03</v>
+        <v>3385.3</v>
       </c>
     </row>
     <row r="43">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>73015.72</v>
+        <v>73209.34</v>
       </c>
     </row>
     <row r="44">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>20077.1</v>
+        <v>20048.94</v>
       </c>
     </row>
     <row r="45">
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>38555.26</v>
+        <v>38604.68</v>
       </c>
     </row>
     <row r="46">
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>13098.26</v>
+        <v>13188.42</v>
       </c>
     </row>
     <row r="47">
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>3025.66</v>
+        <v>3046.49</v>
       </c>
     </row>
     <row r="48">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>30562.25</v>
+        <v>30937.86</v>
       </c>
     </row>
     <row r="49">
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>40813.7</v>
+        <v>41036.9</v>
       </c>
     </row>
     <row r="50">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>62216</v>
+        <v>62556.25</v>
       </c>
     </row>
     <row r="51">
@@ -3562,7 +3562,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>74902.45</v>
+        <v>72989.75999999999</v>
       </c>
     </row>
     <row r="52">
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>7141.48</v>
+        <v>7002.19</v>
       </c>
     </row>
     <row r="53">
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>80602.67</v>
+        <v>78717.10000000001</v>
       </c>
     </row>
     <row r="54">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>6454.18</v>
+        <v>6361.67</v>
       </c>
     </row>
     <row r="55">
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>70298.42999999999</v>
+        <v>70159.98</v>
       </c>
     </row>
     <row r="56">
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>20389.25</v>
+        <v>20349.1</v>
       </c>
     </row>
     <row r="57">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>25114.1</v>
+        <v>25114.26</v>
       </c>
     </row>
     <row r="58">
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>5550.29</v>
+        <v>5546.5</v>
       </c>
     </row>
     <row r="59">
@@ -4050,13 +4050,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>51844.19</v>
+        <v>51666.26</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3355-10-CM26</t>
+          <t>1057432-19-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.101.076-1</t>
+          <t>61.607.100-9</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4111,13 +4111,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1131.82</v>
+        <v>10262.64</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1057432-19-CM26</t>
+          <t>3355-10-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.607.100-9</t>
+          <t>61.101.076-1</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>10317.14</v>
+        <v>1125.84</v>
       </c>
     </row>
     <row r="62">
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2827.64</v>
+        <v>2812.7</v>
       </c>
     </row>
     <row r="63">
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>14144.59</v>
+        <v>14055.95</v>
       </c>
     </row>
     <row r="64">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>31372.75</v>
+        <v>31176.16</v>
       </c>
     </row>
     <row r="65">
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>39147.11</v>
+        <v>39743.08</v>
       </c>
     </row>
     <row r="66">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>41629.67</v>
+        <v>42682.07</v>
       </c>
     </row>
     <row r="67">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1131.27</v>
+        <v>1165.57</v>
       </c>
     </row>
     <row r="68">
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>80602.67</v>
+        <v>83046.8</v>
       </c>
     </row>
     <row r="69">
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>5652.72</v>
+        <v>5820.74</v>
       </c>
     </row>
     <row r="70">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2320.13</v>
+        <v>2311.87</v>
       </c>
     </row>
     <row r="71">
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>7726.04</v>
+        <v>7698.53</v>
       </c>
     </row>
     <row r="72">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>61381.82</v>
+        <v>61698.9</v>
       </c>
     </row>
     <row r="73">
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1092.78</v>
+        <v>1099.98</v>
       </c>
     </row>
     <row r="74">
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>26797.52</v>
+        <v>26974.01</v>
       </c>
     </row>
     <row r="75">
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>24995.44</v>
+        <v>24969.66</v>
       </c>
     </row>
     <row r="76">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>41208.32</v>
+        <v>40965.48</v>
       </c>
     </row>
     <row r="77">
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>40580.15</v>
+        <v>40333.57</v>
       </c>
     </row>
     <row r="78">
@@ -5209,7 +5209,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>13341.3</v>
+        <v>13289.8</v>
       </c>
     </row>
     <row r="79">
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>2192.5</v>
+        <v>2203.85</v>
       </c>
     </row>
     <row r="80">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>78305.89</v>
+        <v>80580.41</v>
       </c>
     </row>
     <row r="81">
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>34436.76</v>
+        <v>35004.33</v>
       </c>
     </row>
     <row r="82">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>29739.75</v>
+        <v>30229.91</v>
       </c>
     </row>
     <row r="83">
@@ -5514,7 +5514,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>7693.21</v>
+        <v>7712.14</v>
       </c>
     </row>
     <row r="84">
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2084.82</v>
+        <v>2070.1</v>
       </c>
     </row>
     <row r="85">
@@ -5636,7 +5636,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2503.33</v>
+        <v>2542.55</v>
       </c>
     </row>
     <row r="86">
@@ -5697,7 +5697,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>22107.95</v>
+        <v>22199.27</v>
       </c>
     </row>
     <row r="87">
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1677.31</v>
+        <v>1672.69</v>
       </c>
     </row>
     <row r="88">
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1216.46</v>
+        <v>1202.42</v>
       </c>
     </row>
     <row r="89">
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>643.15</v>
+        <v>635.73</v>
       </c>
     </row>
     <row r="90">
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>34993.34</v>
+        <v>34792.33</v>
       </c>
     </row>
     <row r="91">
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>7480.27</v>
+        <v>7448.05</v>
       </c>
     </row>
     <row r="92">
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>58248.59</v>
+        <v>57997.66</v>
       </c>
     </row>
     <row r="93">
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>14837.97</v>
+        <v>14623.31</v>
       </c>
     </row>
     <row r="94">
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2747.58</v>
+        <v>2683.64</v>
       </c>
     </row>
     <row r="95">
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>41495.86</v>
+        <v>40530.29</v>
       </c>
     </row>
     <row r="96">
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2088.16</v>
+        <v>2039.57</v>
       </c>
     </row>
     <row r="97">
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3332.27</v>
+        <v>3226.02</v>
       </c>
     </row>
     <row r="98">
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>79353.03999999999</v>
+        <v>76822.72</v>
       </c>
     </row>
     <row r="99">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>602.12</v>
+        <v>590.24</v>
       </c>
     </row>
     <row r="100">
@@ -6551,7 +6551,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>60428.06</v>
+        <v>59236.33</v>
       </c>
     </row>
     <row r="101">
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>13869.64</v>
+        <v>13504.41</v>
       </c>
     </row>
     <row r="102">
@@ -6673,7 +6673,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1058.04</v>
+        <v>1038.85</v>
       </c>
     </row>
     <row r="103">
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>74062.84</v>
+        <v>72079.69</v>
       </c>
     </row>
     <row r="104">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>24992.03</v>
+        <v>24322.83</v>
       </c>
     </row>
     <row r="105">
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>33411.81</v>
+        <v>33509.07</v>
       </c>
     </row>
     <row r="106">
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1049.13</v>
+        <v>1047.38</v>
       </c>
     </row>
     <row r="107">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>30819.96</v>
+        <v>31230.26</v>
       </c>
     </row>
     <row r="108">
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>5784.08</v>
+        <v>5861.08</v>
       </c>
     </row>
     <row r="109">
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1102.59</v>
+        <v>1115.13</v>
       </c>
     </row>
     <row r="110">
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>43301.37</v>
+        <v>43793.8</v>
       </c>
     </row>
     <row r="111">
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>23190.13</v>
+        <v>23263.1</v>
       </c>
     </row>
     <row r="112">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>16155.09</v>
+        <v>16205.92</v>
       </c>
     </row>
     <row r="113">
@@ -7344,7 +7344,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>931.61</v>
+        <v>935.47</v>
       </c>
     </row>
     <row r="114">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>79353.03999999999</v>
+        <v>79517.42999999999</v>
       </c>
     </row>
     <row r="115">
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1582.83</v>
+        <v>1576.03</v>
       </c>
     </row>
     <row r="116">
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>57151.98</v>
+        <v>56374.97</v>
       </c>
     </row>
     <row r="117">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>11998.96</v>
+        <v>11835.83</v>
       </c>
     </row>
     <row r="118">
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>33454.47</v>
+        <v>33634.62</v>
       </c>
     </row>
     <row r="119">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>14712.74</v>
+        <v>14824.18</v>
       </c>
     </row>
     <row r="120">
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>5372.45</v>
+        <v>5413.14</v>
       </c>
     </row>
     <row r="121">
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>4456.14</v>
+        <v>4498.47</v>
       </c>
     </row>
     <row r="122">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1117.6</v>
+        <v>1128.22</v>
       </c>
     </row>
     <row r="123">
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>891.23</v>
+        <v>887.3200000000001</v>
       </c>
     </row>
     <row r="124">
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>13591.62</v>
+        <v>13443.77</v>
       </c>
     </row>
     <row r="125">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>44634.14</v>
+        <v>44148.6</v>
       </c>
     </row>
     <row r="126">
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>68960.99000000001</v>
+        <v>69189.75999999999</v>
       </c>
     </row>
     <row r="127">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2116.67</v>
+        <v>2123.4</v>
       </c>
     </row>
     <row r="128">
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>1782.46</v>
+        <v>1791.93</v>
       </c>
     </row>
     <row r="129">
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>6750.62</v>
+        <v>6829.8</v>
       </c>
     </row>
     <row r="130">
@@ -8381,13 +8381,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>58118.77</v>
+        <v>59101.7</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1057540-1431-CM26</t>
+          <t>4414-726-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.602.198-2</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8442,13 +8442,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>78870.09</v>
+        <v>7704.88</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>4414-726-CM26</t>
+          <t>1057540-1431-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8473,12 +8473,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>61.602.198-2</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>7627.32</v>
+        <v>79672.14</v>
       </c>
     </row>
     <row r="133">
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>32876.37</v>
+        <v>33184.73</v>
       </c>
     </row>
     <row r="134">
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2806.86</v>
+        <v>2759.44</v>
       </c>
     </row>
     <row r="135">
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>73612.08</v>
+        <v>72368.35000000001</v>
       </c>
     </row>
     <row r="136">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>974.83</v>
+        <v>961</v>
       </c>
     </row>
     <row r="137">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>28554.96</v>
+        <v>28377.93</v>
       </c>
     </row>
     <row r="138">
@@ -8869,13 +8869,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>3673.58</v>
+        <v>3650.81</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4414-793-CM26</t>
+          <t>2704-1164-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8895,17 +8895,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8930,13 +8930,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>385.73</v>
+        <v>5727.5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2704-1164-CM26</t>
+          <t>4414-793-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8956,17 +8956,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>5620.64</v>
+        <v>393.06</v>
       </c>
     </row>
     <row r="141">
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>26404.65</v>
+        <v>26906.65</v>
       </c>
     </row>
     <row r="142">
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>276.74</v>
+        <v>278.65</v>
       </c>
     </row>
     <row r="143">
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>41494.43</v>
+        <v>41622.72</v>
       </c>
     </row>
     <row r="144">
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>13283.6</v>
+        <v>13106.66</v>
       </c>
     </row>
     <row r="145">
@@ -9296,7 +9296,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>78949.91</v>
+        <v>79699.85000000001</v>
       </c>
     </row>
     <row r="146">
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>6765</v>
+        <v>6791.41</v>
       </c>
     </row>
     <row r="147">
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>5203.73</v>
+        <v>5224.04</v>
       </c>
     </row>
     <row r="148">
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>45697.47</v>
+        <v>46155.07</v>
       </c>
     </row>
     <row r="149">
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>31902.21</v>
+        <v>32064.78</v>
       </c>
     </row>
     <row r="150">
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2685.37</v>
+        <v>2702.88</v>
       </c>
     </row>
     <row r="151">
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>568.4400000000001</v>
+        <v>569.74</v>
       </c>
     </row>
     <row r="152">
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>470.78</v>
+        <v>473.93</v>
       </c>
     </row>
     <row r="153">
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>14394.45</v>
+        <v>14348.99</v>
       </c>
     </row>
     <row r="154">
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>2353.91</v>
+        <v>2348.79</v>
       </c>
     </row>
     <row r="155">
@@ -9906,7 +9906,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>47009.43</v>
+        <v>46907.15</v>
       </c>
     </row>
     <row r="156">
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>232.66</v>
+        <v>232.15</v>
       </c>
     </row>
     <row r="157">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>214.83</v>
+        <v>214.4</v>
       </c>
     </row>
     <row r="158">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>41988.72</v>
+        <v>41904.55</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>4360-71-CM26</t>
+          <t>554892-5-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10120,12 +10120,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>72.232.500-1</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10150,13 +10150,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>24.78</v>
+        <v>1414.11</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>554892-5-CM26</t>
+          <t>4360-71-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10181,12 +10181,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>72.232.500-1</t>
+          <t>69.170.700-8</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1421.1</v>
+        <v>24.66</v>
       </c>
     </row>
     <row r="161">
@@ -10272,7 +10272,68 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>13833.24</v>
+        <v>13925.83</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>1526410-144-CM26</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>61.102.021-K</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="n">
+        <v>2141.71</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/bio-bio.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/bio-bio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M162"/>
+  <dimension ref="A1:M180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>707422-245-CM25</t>
+          <t>977274-1-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.999.190-7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>846.6799999999999</v>
+        <v>1996.46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>696228-152-CM25</t>
+          <t>1057543-4819-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.607.201-3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO DE SALUD TALCAHUANO HOSPITAL DE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>9119.01</v>
+        <v>57686.46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3361-72-CM25</t>
+          <t>1057540-6794-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.970.300-6</t>
+          <t>61.602.198-2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>372.13</v>
+        <v>75656.22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1057541-1080-CM25</t>
+          <t>1057415-155-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>56667.52</v>
+        <v>12298.17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3737-289-CM25</t>
+          <t>1057541-319-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.170.300-2</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAJA</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1291.4</v>
+        <v>1421.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1057422-760-CM25</t>
+          <t>4034-288-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.607.307-9</t>
+          <t>69.160.501-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>22209.9</v>
+        <v>911.24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3355-502-CM25</t>
+          <t>2102-489-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.101.076-1</t>
+          <t>61.602.212-1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1622.12</v>
+        <v>30437.46</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3355-506-CM25</t>
+          <t>4375-1691-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.101.076-1</t>
+          <t>61.602.189-3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2138.8</v>
+        <v>3405.27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1057540-20660-CM25</t>
+          <t>1057415-285-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.602.198-2</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>76049.48</v>
+        <v>23050.08</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1057415-583-CM25</t>
+          <t>1057541-560-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>22414.59</v>
+        <v>278.77</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>860729-17-CM25</t>
+          <t>1057422-465-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>61.607.307-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>672.71</v>
+        <v>20736.45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2672-42-CM25</t>
+          <t>972135-12-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.150.400-k</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>24052.81</v>
+        <v>15598.09</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1057541-1120-CM25</t>
+          <t>1057541-824-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>61579.68</v>
+        <v>50722.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>973168-21-CM25</t>
+          <t>4375-2883-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.803.435-8</t>
+          <t>61.602.189-3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SII Oficina de Bienestar</t>
+          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>130.46</v>
+        <v>1198.56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>973168-18-CM25</t>
+          <t>554892-5-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,27 +1378,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.803.435-8</t>
+          <t>72.232.500-1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SII Oficina de Bienestar</t>
+          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>739.27</v>
+        <v>323.29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>973168-19-CM25</t>
+          <t>1057415-537-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.803.435-8</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SII Oficina de Bienestar</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1043.68</v>
+        <v>21061.01</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>973168-20-CM25</t>
+          <t>1576-312-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.803.435-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SII Oficina de Bienestar</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>478.35</v>
+        <v>2445.06</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>891-61-CM25</t>
+          <t>2102-992-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.602.212-1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>56.67</v>
+        <v>34995.04</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1057420-980-CM25</t>
+          <t>707422-245-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.607.305-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>21401.93</v>
+        <v>846.6799999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4494-798-CM25</t>
+          <t>696228-152-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>26647.74</v>
+        <v>9119.01</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4034-1104-CM25</t>
+          <t>3361-72-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,22 +1749,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.160.501-9</t>
+          <t>61.970.300-6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1066.83</v>
+        <v>372.13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>995118-165-CM25</t>
+          <t>1057541-1080-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>VIII Zona de Carabineros Bio Bío</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2963.03</v>
+        <v>56667.52</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3220-911-CM25</t>
+          <t>3737-289-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,22 +1871,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.102.021-k</t>
+          <t>69.170.300-2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIa. ZONA NAVAL</t>
+          <t>I MUNICIPALIDAD DE LAJA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>25508.05</v>
+        <v>1291.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>652-485-CM25</t>
+          <t>1057422-760-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>61.607.307-9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>40300.46</v>
+        <v>22209.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3355-532-CM25</t>
+          <t>3355-506-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1708.56</v>
+        <v>2138.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1070329-432-CM25</t>
+          <t>3355-502-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>61.101.076-1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>13836.91</v>
+        <v>1622.12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2704-2510-CM25</t>
+          <t>860729-17-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,22 +2115,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5446.4</v>
+        <v>672.71</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3355-534-CM25</t>
+          <t>1057540-20660-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.101.076-1</t>
+          <t>61.602.198-2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>24906.9</v>
+        <v>76049.48</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2102-1114-CM25</t>
+          <t>1057415-583-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.602.212-1</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>40243.67</v>
+        <v>22414.59</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1057736-100-CM25</t>
+          <t>1057541-1120-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,17 +2293,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>153.53</v>
+        <v>61579.68</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4375-4279-CM25</t>
+          <t>2672-42-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.602.189-3</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>17887.76</v>
+        <v>24052.81</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4494-871-CM25</t>
+          <t>973168-21-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,27 +2415,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>60.803.435-8</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>SII Oficina de Bienestar</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>12752.82</v>
+        <v>130.46</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4494-875-CM25</t>
+          <t>973168-20-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,27 +2476,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>60.803.435-8</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>SII Oficina de Bienestar</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>10525.29</v>
+        <v>478.35</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4494-877-CM25</t>
+          <t>973168-18-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,27 +2537,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>60.803.435-8</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>SII Oficina de Bienestar</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>4814.82</v>
+        <v>739.27</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1057415-638-CM25</t>
+          <t>973168-19-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>60.803.435-8</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>SII Oficina de Bienestar</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>24144.61</v>
+        <v>1043.68</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1057422-850-CM25</t>
+          <t>1057420-980-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.607.307-9</t>
+          <t>61.607.305-2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1372.5</v>
+        <v>21401.93</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1057422-852-CM25</t>
+          <t>891-61-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.607.307-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>20822.54</v>
+        <v>56.67</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1349-163-CM25</t>
+          <t>4494-798-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,27 +2781,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.002.019-4</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>21452.03</v>
+        <v>26647.74</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>554892-6-CM25</t>
+          <t>4034-1104-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>72.232.500-1</t>
+          <t>69.160.501-9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
+          <t>Ilustre Municipalidad de Cañete - Educación</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>7643.67</v>
+        <v>1066.83</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3796-632-CM25</t>
+          <t>652-485-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.172.600-2</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILACO</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>18661.13</v>
+        <v>40300.46</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>995118-202-CM25</t>
+          <t>1070329-432-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>VIII Zona de Carabineros Bio Bío</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3385.3</v>
+        <v>13836.91</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1377-54-SE25</t>
+          <t>3355-532-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,27 +3025,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>65.002.110-k</t>
+          <t>61.101.076-1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>CORPORACIÓN DE FOMENTO DE LA PRODUCCIÓN - CORFO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3063,24 +3063,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>73209.34</v>
+        <v>1708.56</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1057420-8840-CM25</t>
+          <t>3220-911-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3090,12 +3086,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3105,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.607.305-2</t>
+          <t>61.102.021-k</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
+          <t>COMANDANCIA EN JEFE DE LA IIa. ZONA NAVAL</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3135,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>20048.94</v>
+        <v>25508.05</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>652-515-CM25</t>
+          <t>995118-165-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3151,12 +3147,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3166,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>VIII Zona de Carabineros Bio Bío</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3196,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>38604.68</v>
+        <v>2963.03</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1070329-460-CM25</t>
+          <t>2704-2510-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3212,12 +3208,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3227,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3257,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>13188.42</v>
+        <v>5446.4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4358-365-CM25</t>
+          <t>3355-534-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3273,27 +3269,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.170.701-6</t>
+          <t>61.101.076-1</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3318,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>3046.49</v>
+        <v>24906.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4055-717-CM25</t>
+          <t>2102-1114-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3334,27 +3330,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.150.900-1</t>
+          <t>61.602.212-1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUMBEL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3379,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>30937.86</v>
+        <v>40243.67</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2102-1200-CM25</t>
+          <t>1057736-100-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3400,22 +3396,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.602.212-1</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3440,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>41036.9</v>
+        <v>153.53</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1057541-1250-CM25</t>
+          <t>4375-4279-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3461,7 +3457,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3471,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>61.602.189-3</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3501,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>62556.25</v>
+        <v>17887.76</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4375-4633-CM25</t>
+          <t>1057415-638-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3517,12 +3513,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3532,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.602.189-3</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3562,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>72989.75999999999</v>
+        <v>24144.61</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1057736-2-CM26</t>
+          <t>4494-875-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3578,12 +3574,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3593,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3623,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>7002.19</v>
+        <v>10525.29</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1057540-21-CM26</t>
+          <t>4494-871-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3639,27 +3635,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.602.198-2</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3684,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>78717.10000000001</v>
+        <v>12752.82</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4358-3-CM26</t>
+          <t>4494-877-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3700,27 +3696,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.170.701-6</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3745,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>6361.67</v>
+        <v>4814.82</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1057422-3-CM26</t>
+          <t>1057422-850-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3761,12 +3757,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3806,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>70159.98</v>
+        <v>1372.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1057420-21-CM26</t>
+          <t>1057422-852-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3822,12 +3818,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3837,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.607.305-2</t>
+          <t>61.607.307-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3867,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>20349.1</v>
+        <v>20822.54</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1057415-2749-CM26</t>
+          <t>1349-163-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3883,12 +3879,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3898,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>61.002.019-4</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3928,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>25114.26</v>
+        <v>21452.03</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4358-20-CM26</t>
+          <t>554892-6-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3944,27 +3940,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.170.701-6</t>
+          <t>72.232.500-1</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3989,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>5546.5</v>
+        <v>7643.67</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>732434-4-CM26</t>
+          <t>3796-632-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4005,12 +4001,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4020,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>65.913.720-8</t>
+          <t>69.172.600-2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Centro de Sangre y Tejidos de Concepcion</t>
+          <t>I MUNICIPALIDAD DE QUILACO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4050,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>51666.26</v>
+        <v>18661.13</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1057432-19-CM26</t>
+          <t>995118-202-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4066,12 +4062,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4081,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.607.100-9</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>VIII Zona de Carabineros Bio Bío</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4111,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>10262.64</v>
+        <v>3385.3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3355-10-CM26</t>
+          <t>1377-54-SE25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4127,27 +4123,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.101.076-1</t>
+          <t>65.002.110-k</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>CORPORACIÓN DE FOMENTO DE LA PRODUCCIÓN - CORFO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4165,20 +4161,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1125.84</v>
+        <v>73209.34</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3355-9-CM26</t>
+          <t>1057420-8840-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.101.076-1</t>
+          <t>61.607.305-2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4233,13 +4233,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2812.7</v>
+        <v>20048.94</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1070329-3-CM26</t>
+          <t>652-515-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4294,13 +4294,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>14055.95</v>
+        <v>38604.68</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3220-14-CM26</t>
+          <t>4358-365-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4310,27 +4310,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.102.021-k</t>
+          <t>69.170.701-6</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIa. ZONA NAVAL</t>
+          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>31176.16</v>
+        <v>3046.49</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>652-29-CM26</t>
+          <t>1070329-460-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4416,13 +4416,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>39743.08</v>
+        <v>13188.42</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2102-38-CM26</t>
+          <t>4055-717-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4432,27 +4432,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.602.212-1</t>
+          <t>69.150.900-1</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+          <t>I MUNICIPALIDAD DE YUMBEL</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4477,13 +4477,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>42682.07</v>
+        <v>30937.86</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3382-21-CM26</t>
+          <t>2102-1200-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4493,12 +4493,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>65.311.270-K</t>
+          <t>61.602.212-1</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>CENTRO CLINICO MILITAR CONCEPCION</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4538,13 +4538,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1165.57</v>
+        <v>41036.9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1057540-272-CM26</t>
+          <t>1057541-1250-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4554,12 +4554,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.602.198-2</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>83046.8</v>
+        <v>62556.25</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2421-106-CM26</t>
+          <t>4375-4633-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4620,22 +4620,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.256.900-8</t>
+          <t>61.602.189-3</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dirección de Administración de Salud Municipal</t>
+          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4660,13 +4660,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>5820.74</v>
+        <v>72989.75999999999</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4074-4-CM26</t>
+          <t>1057736-2-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.150.902-8</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Yumbel - Depto. Educacion</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4721,13 +4721,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2311.87</v>
+        <v>7002.19</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4074-3-CM26</t>
+          <t>1057540-21-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4737,27 +4737,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.150.902-8</t>
+          <t>61.602.198-2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Yumbel - Depto. Educacion</t>
+          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4782,13 +4782,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>7698.53</v>
+        <v>78717.10000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1057541-136-CM26</t>
+          <t>4358-3-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>69.170.701-6</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4843,13 +4843,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>61698.9</v>
+        <v>6361.67</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4462-85-CM26</t>
+          <t>1057422-3-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>61.607.307-9</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4904,13 +4904,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1099.98</v>
+        <v>70159.98</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1057415-2789-CM26</t>
+          <t>1057420-21-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4920,12 +4920,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4935,12 +4935,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>61.607.305-2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4965,13 +4965,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>26974.01</v>
+        <v>20349.1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1057420-116-CM26</t>
+          <t>1057415-2749-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.607.305-2</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5026,13 +5026,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>24969.66</v>
+        <v>25114.26</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2102-105-CM26</t>
+          <t>4358-20-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5042,12 +5042,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5057,12 +5057,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.602.212-1</t>
+          <t>69.170.701-6</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>40965.48</v>
+        <v>5546.5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>652-50-CM26</t>
+          <t>732434-4-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>65.913.720-8</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>Centro de Sangre y Tejidos de Concepcion</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5148,13 +5148,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>40333.57</v>
+        <v>51666.26</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1070329-41-CM26</t>
+          <t>3355-9-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5164,12 +5164,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>61.101.076-1</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5209,13 +5209,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>13289.8</v>
+        <v>2812.7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3355-56-CM26</t>
+          <t>3355-10-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5225,12 +5225,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5270,13 +5270,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>2203.85</v>
+        <v>1125.84</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1057540-566-CM26</t>
+          <t>1057432-19-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5286,12 +5286,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.602.198-2</t>
+          <t>61.607.100-9</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5331,13 +5331,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>80580.41</v>
+        <v>10262.64</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1057541-213-CM26</t>
+          <t>1070329-3-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5392,13 +5392,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>35004.33</v>
+        <v>14055.95</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1057415-2819-CM26</t>
+          <t>3220-14-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>61.102.021-k</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>COMANDANCIA EN JEFE DE LA IIa. ZONA NAVAL</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5453,13 +5453,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>30229.91</v>
+        <v>31176.16</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4075-36-CM26</t>
+          <t>652-29-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5469,27 +5469,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.150.901-K</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Yumbel - Depto. Salud</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5514,13 +5514,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>7712.14</v>
+        <v>39743.08</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1057422-169-CM26</t>
+          <t>2102-38-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.607.307-9</t>
+          <t>61.602.212-1</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5575,13 +5575,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2070.1</v>
+        <v>42682.07</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1143-24-CM26</t>
+          <t>3382-21-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5591,27 +5591,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>60.511.080-0</t>
+          <t>65.311.270-K</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL BIOBÍO</t>
+          <t>CENTRO CLINICO MILITAR CONCEPCION</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5636,13 +5636,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2542.55</v>
+        <v>1165.57</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1057420-194-CM26</t>
+          <t>1057540-272-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.607.305-2</t>
+          <t>61.602.198-2</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
+          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5697,13 +5697,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>22199.27</v>
+        <v>83046.8</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2230-4-CM26</t>
+          <t>2421-106-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5713,27 +5713,27 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.941.900-6</t>
+          <t>69.256.900-8</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>DEFENSORIA PENAL PUBLICA</t>
+          <t>Dirección de Administración de Salud Municipal</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5758,13 +5758,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1672.69</v>
+        <v>5820.74</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>554892-2-CM26</t>
+          <t>4074-3-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>72.232.500-1</t>
+          <t>69.150.902-8</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
+          <t>Ilustre Municipalidad de Yumbel - Depto. Educacion</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5819,13 +5819,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1202.42</v>
+        <v>7698.53</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4462-137-CM26</t>
+          <t>4074-4-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5835,27 +5835,27 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>69.150.902-8</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>Ilustre Municipalidad de Yumbel - Depto. Educacion</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5880,13 +5880,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>635.73</v>
+        <v>2311.87</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>652-96-CM26</t>
+          <t>1057541-136-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5911,12 +5911,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5941,13 +5941,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>34792.33</v>
+        <v>61698.9</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1576-42-CM26</t>
+          <t>1057415-2789-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5957,12 +5957,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6002,13 +6002,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>7448.05</v>
+        <v>26974.01</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1576-41-CM26</t>
+          <t>4462-85-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6063,13 +6063,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>57997.66</v>
+        <v>1099.98</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1070329-81-CM26</t>
+          <t>1057420-116-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6079,12 +6079,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>61.607.305-2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6124,13 +6124,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>14623.31</v>
+        <v>24969.66</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3365-36-CM26</t>
+          <t>2102-105-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6140,12 +6140,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.962.000-3</t>
+          <t>61.602.212-1</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2683.64</v>
+        <v>40965.48</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2102-242-CM26</t>
+          <t>652-50-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.602.212-1</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6246,13 +6246,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>40530.29</v>
+        <v>40333.57</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1057541-276-CM26</t>
+          <t>1070329-41-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6307,13 +6307,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2039.57</v>
+        <v>13289.8</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>654-105-CM26</t>
+          <t>3355-56-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6323,12 +6323,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.820.004-3</t>
+          <t>61.101.076-1</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6368,13 +6368,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3226.02</v>
+        <v>2203.85</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1057540-928-CM26</t>
+          <t>1057540-566-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6429,13 +6429,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>76822.72</v>
+        <v>80580.41</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>4434-5-CM26</t>
+          <t>1057415-2819-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6445,12 +6445,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>590.24</v>
+        <v>30229.91</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1057541-289-CM26</t>
+          <t>1057541-213-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6551,13 +6551,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>59236.33</v>
+        <v>35004.33</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>707422-50-CM26</t>
+          <t>4075-36-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6567,27 +6567,27 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.150.901-K</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Ilustre Municipalidad de Yumbel - Depto. Salud</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6612,13 +6612,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>13504.41</v>
+        <v>7712.14</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1057541-292-CM26</t>
+          <t>1057422-169-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6628,12 +6628,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6643,12 +6643,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>61.607.307-9</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6673,13 +6673,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1038.85</v>
+        <v>2070.1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1057422-238-CM26</t>
+          <t>1143-24-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6689,27 +6689,27 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.607.307-9</t>
+          <t>60.511.080-0</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL BIOBÍO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6734,13 +6734,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>72079.69</v>
+        <v>2542.55</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1057415-2882-CM26</t>
+          <t>1057420-194-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6765,12 +6765,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>61.607.305-2</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6795,13 +6795,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>24322.83</v>
+        <v>22199.27</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>4055-125-CM26</t>
+          <t>2230-4-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6811,27 +6811,27 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>69.150.900-1</t>
+          <t>61.941.900-6</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUMBEL</t>
+          <t>DEFENSORIA PENAL PUBLICA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6856,13 +6856,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>33509.07</v>
+        <v>1672.69</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>4462-175-CM26</t>
+          <t>554892-2-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6872,27 +6872,27 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>72.232.500-1</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6917,13 +6917,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1047.38</v>
+        <v>1202.42</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>4238-82-CM26</t>
+          <t>4462-137-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>69.160.202-8</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Curanilahue - Salud</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6978,13 +6978,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>31230.26</v>
+        <v>635.73</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>707422-56-CM26</t>
+          <t>652-96-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6994,12 +6994,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7009,12 +7009,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7039,13 +7039,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>5861.08</v>
+        <v>34792.33</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1057415-2891-CM26</t>
+          <t>1576-41-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7055,12 +7055,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7100,13 +7100,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1115.13</v>
+        <v>57997.66</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>652-117-CM26</t>
+          <t>1576-42-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7131,12 +7131,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7161,13 +7161,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>43793.8</v>
+        <v>7448.05</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2102-322-CM26</t>
+          <t>1070329-81-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7177,12 +7177,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.602.212-1</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7222,13 +7222,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>23263.1</v>
+        <v>14623.31</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1070329-115-CM26</t>
+          <t>2102-242-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>61.602.212-1</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7283,13 +7283,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>16205.92</v>
+        <v>40530.29</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>995118-48-CM26</t>
+          <t>1057541-276-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7314,12 +7314,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>VIII Zona de Carabineros Bio Bío</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7344,13 +7344,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>935.47</v>
+        <v>2039.57</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1057540-1162-CM26</t>
+          <t>3365-36-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7360,12 +7360,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.602.198-2</t>
+          <t>61.962.000-3</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7405,13 +7405,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>79517.42999999999</v>
+        <v>2683.64</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>4377-146-CM26</t>
+          <t>654-105-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7426,22 +7426,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.151.100-6</t>
+          <t>61.820.004-3</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ROSENDO</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7466,13 +7466,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1576.03</v>
+        <v>3226.02</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1057541-390-CM26</t>
+          <t>1057540-928-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7497,12 +7497,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>61.602.198-2</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7527,13 +7527,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>56374.97</v>
+        <v>76822.72</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>707422-68-CM26</t>
+          <t>4434-5-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7543,12 +7543,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Servicio Nacional del Patrimonio Cultural</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7588,13 +7588,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>11835.83</v>
+        <v>590.24</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1057415-2914-CM26</t>
+          <t>1057541-289-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7649,13 +7649,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>33634.62</v>
+        <v>59236.33</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>4414-575-CM26</t>
+          <t>707422-50-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7680,12 +7680,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7710,13 +7710,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>14824.18</v>
+        <v>13504.41</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>4414-578-CM26</t>
+          <t>1057541-292-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7726,12 +7726,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7771,13 +7771,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>5413.14</v>
+        <v>1038.85</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1057414-340-CM26</t>
+          <t>1057422-238-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.607.300-1</t>
+          <t>61.607.307-9</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7832,13 +7832,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>4498.47</v>
+        <v>72079.69</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>995118-60-CM26</t>
+          <t>1057415-2882-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>VIII Zona de Carabineros Bio Bío</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1128.22</v>
+        <v>24322.83</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1550-9-CM26</t>
+          <t>4055-125-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7909,27 +7909,27 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>69.150.900-1</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>I MUNICIPALIDAD DE YUMBEL</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7954,13 +7954,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>887.3200000000001</v>
+        <v>33509.07</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1070329-135-CM26</t>
+          <t>4462-175-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8015,13 +8015,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>13443.77</v>
+        <v>1047.38</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>652-146-CM26</t>
+          <t>4238-82-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>69.160.202-8</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>Ilustre Municipalidad de Curanilahue - Salud</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8076,13 +8076,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>44148.6</v>
+        <v>31230.26</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2102-416-CM26</t>
+          <t>707422-56-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8107,12 +8107,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.602.212-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8137,13 +8137,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>69189.75999999999</v>
+        <v>5861.08</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1077234-1-CM26</t>
+          <t>1057415-2891-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8153,27 +8153,27 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2123.4</v>
+        <v>1115.13</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1057414-382-CM26</t>
+          <t>652-117-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8229,12 +8229,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.607.300-1</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8259,13 +8259,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>1791.93</v>
+        <v>43793.8</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>4414-707-CM26</t>
+          <t>1070329-115-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8320,13 +8320,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>6829.8</v>
+        <v>16205.92</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1057541-461-CM26</t>
+          <t>2102-322-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>61.602.212-1</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8381,13 +8381,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>59101.7</v>
+        <v>23263.1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>4414-726-CM26</t>
+          <t>995118-48-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>VIII Zona de Carabineros Bio Bío</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8442,13 +8442,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>7704.88</v>
+        <v>935.47</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1057540-1431-CM26</t>
+          <t>1057540-1162-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8503,13 +8503,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>79672.14</v>
+        <v>79517.42999999999</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1057415-2983-CM26</t>
+          <t>4377-146-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8519,27 +8519,27 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>69.151.100-6</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>I MUNICIPALIDAD DE SAN ROSENDO</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8564,13 +8564,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>33184.73</v>
+        <v>1576.03</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>831-145-CM26</t>
+          <t>1057541-390-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8595,12 +8595,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>72.232.500-1</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8625,13 +8625,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2759.44</v>
+        <v>56374.97</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1057422-368-CM26</t>
+          <t>707422-68-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8656,12 +8656,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.607.307-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8686,13 +8686,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>72368.35000000001</v>
+        <v>11835.83</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>995118-82-CM26</t>
+          <t>1057415-2914-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8702,12 +8702,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>VIII Zona de Carabineros Bio Bío</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8747,13 +8747,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>961</v>
+        <v>33634.62</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2410-266-CM26</t>
+          <t>4414-575-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8763,27 +8763,27 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8808,13 +8808,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>28377.93</v>
+        <v>14824.18</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>831-158-CM26</t>
+          <t>4414-578-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8839,12 +8839,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>72.232.500-1</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8869,13 +8869,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>3650.81</v>
+        <v>5413.14</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2704-1164-CM26</t>
+          <t>995118-60-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8885,27 +8885,27 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>VIII Zona de Carabineros Bio Bío</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8930,13 +8930,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>5727.5</v>
+        <v>1128.22</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>4414-793-CM26</t>
+          <t>1057414-340-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8991,13 +8991,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>393.06</v>
+        <v>4498.47</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>732434-161-CM26</t>
+          <t>1550-9-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>65.913.720-8</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Centro de Sangre y Tejidos de Concepcion</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9052,13 +9052,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>26906.65</v>
+        <v>887.3200000000001</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>4474-579-CM26</t>
+          <t>1070329-135-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9068,27 +9068,27 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>69.160.600-7</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONTULMO</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9113,28 +9113,28 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>278.65</v>
+        <v>13443.77</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>652-173-CM26</t>
+          <t>652-146-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9174,28 +9174,28 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>41622.72</v>
+        <v>44148.6</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1070329-170-CM26</t>
+          <t>2102-416-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>61.602.212-1</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9235,43 +9235,43 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>13106.66</v>
+        <v>69189.75999999999</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1057540-1639-CM26</t>
+          <t>1077234-1-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.602.198-2</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9296,43 +9296,43 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>79699.85000000001</v>
+        <v>2123.4</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>4491-322-CM26</t>
+          <t>1057414-382-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>69.150.501-4</t>
+          <t>61.607.300-1</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Penco - Educación</t>
+          <t>SERVICIO DE SALUD BIO BIO</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9357,43 +9357,43 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>6791.41</v>
+        <v>1791.93</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>4491-323-CM26</t>
+          <t>4414-707-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>69.150.501-4</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Penco - Educación</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9418,28 +9418,28 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>5224.04</v>
+        <v>6829.8</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>4375-1850-CM26</t>
+          <t>1057541-461-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9449,12 +9449,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.602.189-3</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9479,28 +9479,28 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>46155.07</v>
+        <v>59101.7</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1057415-3043-CM26</t>
+          <t>1057540-1431-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9510,12 +9510,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.602.220-2</t>
+          <t>61.602.198-2</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9540,43 +9540,43 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>32064.78</v>
+        <v>79672.14</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5557-38-CM26</t>
+          <t>4414-726-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9601,28 +9601,28 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2702.88</v>
+        <v>7704.88</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>995118-100-CM26</t>
+          <t>1057415-2983-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9632,12 +9632,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>61.602.220-2</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>VIII Zona de Carabineros Bio Bío</t>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9662,43 +9662,43 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>569.74</v>
+        <v>33184.73</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>4360-67-CM26</t>
+          <t>831-145-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>72.232.500-1</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9723,28 +9723,28 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>473.93</v>
+        <v>2759.44</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1070329-198-CM26</t>
+          <t>1057422-368-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>61.607.307-9</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9784,43 +9784,43 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>14348.99</v>
+        <v>72368.35000000001</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>4359-133-CM26</t>
+          <t>995118-82-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>VIII Zona de Carabineros Bio Bío</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9845,43 +9845,43 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>2348.79</v>
+        <v>961</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2102-606-CM26</t>
+          <t>2410-266-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.602.212-1</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9906,28 +9906,28 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>46907.15</v>
+        <v>28377.93</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1057422-511-CM26</t>
+          <t>831-158-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.607.307-9</t>
+          <t>72.232.500-1</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
+          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9967,28 +9967,28 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>232.15</v>
+        <v>3650.81</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>973168-5-CM26</t>
+          <t>4414-793-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9998,12 +9998,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>60.803.435-8</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>SII Oficina de Bienestar</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10028,43 +10028,43 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>214.4</v>
+        <v>393.06</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>652-201-CM26</t>
+          <t>2704-1164-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10089,43 +10089,43 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>41904.55</v>
+        <v>5727.5</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>554892-5-CM26</t>
+          <t>732434-161-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>72.232.500-1</t>
+          <t>65.913.720-8</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
+          <t>Centro de Sangre y Tejidos de Concepcion</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10150,28 +10150,28 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>1414.11</v>
+        <v>26906.65</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>4360-71-CM26</t>
+          <t>4474-579-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10181,12 +10181,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>69.160.600-7</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>I MUNICIPALIDAD DE CONTULMO</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10211,13 +10211,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>24.66</v>
+        <v>278.65</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>4351-341-CM26</t>
+          <t>652-173-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10227,27 +10227,27 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>69.170.700-8</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10272,13 +10272,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>13925.83</v>
+        <v>41622.72</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1526410-144-CM26</t>
+          <t>1070329-170-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10288,27 +10288,27 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.102.021-K</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10333,6 +10333,1104 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
+        <v>13106.66</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>1057540-1639-CM26</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>61.602.198-2</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="n">
+        <v>79699.85000000001</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>4491-322-CM26</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>69.150.501-4</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Penco - Educación</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="n">
+        <v>6791.41</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>4491-323-CM26</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>69.150.501-4</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Penco - Educación</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="n">
+        <v>5224.04</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>4375-1850-CM26</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>61.602.189-3</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="n">
+        <v>46155.07</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>1057415-3043-CM26</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>61.602.220-2</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD BIO BIO HOSPITAL NACIMIENTO</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="n">
+        <v>32064.78</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>5557-38-CM26</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>61.533.000-0</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="n">
+        <v>2702.88</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>995118-100-CM26</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>61.954.400-5</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>VIII Zona de Carabineros Bio Bío</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="n">
+        <v>569.74</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>4360-67-CM26</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>69.170.700-8</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="n">
+        <v>473.93</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>1070329-198-CM26</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>61.980.370-1</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>CESFAM LIRQUEN</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="n">
+        <v>14348.99</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>4359-133-CM26</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>69.170.700-8</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="n">
+        <v>2348.79</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2102-606-CM26</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>61.602.212-1</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="n">
+        <v>46907.15</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>1057422-511-CM26</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>61.607.307-9</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE YU</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="n">
+        <v>232.15</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>973168-5-CM26</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>60.803.435-8</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>SII Oficina de Bienestar</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="n">
+        <v>214.4</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>652-201-CM26</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>61.954.500-1</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCO</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="n">
+        <v>41904.55</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>554892-5-CM26</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>72.232.500-1</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE LA REGION DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="n">
+        <v>1414.11</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>4360-71-CM26</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>69.170.700-8</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="n">
+        <v>24.66</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>4351-341-CM26</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>69.170.700-8</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="n">
+        <v>13925.83</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>1526410-144-CM26</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>61.102.021-K</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="n">
         <v>2141.71</v>
       </c>
     </row>
